--- a/artfynd/A 25062-2026 artfynd.xlsx
+++ b/artfynd/A 25062-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2678987</v>
+        <v>501842</v>
       </c>
       <c r="B2" t="n">
-        <v>96360</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219864</v>
+        <v>1654</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Veronica montana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>398725.9978122326</v>
+        <v>398726</v>
       </c>
       <c r="R2" t="n">
-        <v>6150039.645668292</v>
+        <v>6150040</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2007-05-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2007-05-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,50 +777,55 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3440992</v>
+        <v>61734913</v>
       </c>
       <c r="B3" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>3483</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Rutbläcksvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Coprinopsis picacea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Bull.:Fr.) Redhead, Vilgalys &amp; Moncalvo</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Havgård: 500 m väster om Gudmundtorp, Sk</t>
+          <t>Gabeljung Norr, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398725.9978122326</v>
+        <v>398731</v>
       </c>
       <c r="R3" t="n">
-        <v>6150039.645668292</v>
+        <v>6149966</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,22 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2007-04-19</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2007-04-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,55 +866,46 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Askskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mats Gustavsson</t>
+          <t>Yvonne Nord</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mats Gustavsson</t>
+          <t>Yvonne Nord, Bo Nylander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4806382</v>
+        <v>2217567</v>
       </c>
       <c r="B4" t="n">
-        <v>101679</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>219711</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -949,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>398725.9978122326</v>
+        <v>398726</v>
       </c>
       <c r="R4" t="n">
-        <v>6150039.645668292</v>
+        <v>6150040</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,22 +950,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2007-04-19</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-05-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2007-04-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-05-18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,53 +987,52 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>501842</v>
+        <v>127693676</v>
       </c>
       <c r="B5" t="n">
-        <v>104014</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1654</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Veronica montana</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Havgård: 500 m väster om Gudmundtorp, Sk</t>
+          <t>Hunneröd, 750m SSV, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>398725.9978122326</v>
+        <v>398773</v>
       </c>
       <c r="R5" t="n">
-        <v>6150039.645668292</v>
+        <v>6149975</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,22 +1056,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2007-05-18</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2007-05-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,38 +1070,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Askskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mats Gustavsson</t>
+          <t>Ola Elleström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mats Gustavsson</t>
+          <t>Ola Elleström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2217567</v>
+        <v>2678987</v>
       </c>
       <c r="B6" t="n">
-        <v>108193</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99147</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,16 +1100,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219711</v>
+        <v>219864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1183,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>398725.9978122326</v>
+        <v>398726</v>
       </c>
       <c r="R6" t="n">
-        <v>6150039.645668292</v>
+        <v>6150040</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,19 +1157,9 @@
           <t>2007-05-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2007-05-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,15 +1191,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4755275</v>
+        <v>118734413</v>
       </c>
       <c r="B7" t="n">
-        <v>96184</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107719</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,37 +1202,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221918</v>
+        <v>220015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lundvårlök</t>
+          <t>Hässleklocka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gagea spathacea</t>
+          <t>Campanula latifolia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hayne) Salisb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Havgård: 500 m väster om Gudmundtorp, Sk</t>
+          <t>Hunneröd, 750m SSV, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>398725.9978122326</v>
+        <v>398773</v>
       </c>
       <c r="R7" t="n">
-        <v>6150039.645668292</v>
+        <v>6149975</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,22 +1264,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2007-04-19</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2007-04-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,73 +1278,64 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Askskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mats Gustavsson</t>
+          <t>Ola Elleström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mats Gustavsson</t>
+          <t>Ola Elleström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3784396</v>
+        <v>2430227</v>
       </c>
       <c r="B8" t="n">
-        <v>103345</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221423</v>
+        <v>220075</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Havgård: väster om Gudmundtorp, Sk</t>
+          <t>Havgård: 500 m väster om Gudmundtorp, Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>398834.8525036477</v>
+        <v>398726</v>
       </c>
       <c r="R8" t="n">
-        <v>6149957.80308234</v>
+        <v>6150040</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,21 +1365,11 @@
           <t>2007-04-19</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2007-04-19</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1476,7 +1381,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Skogsväg</t>
+          <t>Askskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1494,37 +1399,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3924727</v>
+        <v>3440992</v>
       </c>
       <c r="B9" t="n">
-        <v>99397</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221235</v>
+        <v>220785</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1534,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>398725.9978122326</v>
+        <v>398726</v>
       </c>
       <c r="R9" t="n">
-        <v>6150039.645668292</v>
+        <v>6150040</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,22 +1464,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2007-05-18</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-04-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2007-05-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-04-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,60 +1501,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>61734913</v>
+        <v>3924727</v>
       </c>
       <c r="B10" t="n">
-        <v>87558</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3483</v>
+        <v>221235</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rutbläcksvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Coprinopsis picacea</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bull.:Fr.) Redhead, Vilgalys &amp; Moncalvo</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gabeljung Norr, Sk</t>
+          <t>Havgård: 500 m väster om Gudmundtorp, Sk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>398730.5439664493</v>
+        <v>398726</v>
       </c>
       <c r="R10" t="n">
-        <v>6149965.873267072</v>
+        <v>6150040</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1691,22 +1566,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2016-10-12</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-05-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2016-10-12</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-05-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,34 +1580,33 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Askskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Yvonne Nord</t>
+          <t>Mats Gustavsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Yvonne Nord, Bo Nylander</t>
+          <t>Mats Gustavsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118734413</v>
+        <v>3784396</v>
       </c>
       <c r="B11" t="n">
-        <v>106394</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106329</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1750,45 +1614,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220015</v>
+        <v>221423</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hässleklocka</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Campanula latifolia</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hunneröd, 750m SSV, Sk</t>
+          <t>Havgård: väster om Gudmundtorp, Sk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>398773</v>
+        <v>398835</v>
       </c>
       <c r="R11" t="n">
-        <v>6149975</v>
+        <v>6149958</v>
       </c>
       <c r="S11" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1812,12 +1668,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2007-04-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2007-04-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1826,76 +1682,71 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Skogsväg</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ola Elleström</t>
+          <t>Mats Gustavsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ola Elleström</t>
+          <t>Mats Gustavsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118734410</v>
+        <v>4755275</v>
       </c>
       <c r="B12" t="n">
-        <v>99182</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>224698</v>
+        <v>221918</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lundäxing</t>
+          <t>Lundvårlök</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylis polygama</t>
+          <t>Gagea spathacea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Horv.</t>
+          <t>(Hayne) Salisb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hunneröd, 750m SSV, Sk</t>
+          <t>Havgård: 500 m väster om Gudmundtorp, Sk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>398773</v>
+        <v>398726</v>
       </c>
       <c r="R12" t="n">
-        <v>6149975</v>
+        <v>6150040</v>
       </c>
       <c r="S12" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1919,12 +1770,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2007-04-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2007-04-19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1933,19 +1784,23 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Askskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ola Elleström</t>
+          <t>Mats Gustavsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ola Elleström</t>
+          <t>Mats Gustavsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1955,12 +1810,7 @@
         <v>118734419</v>
       </c>
       <c r="B13" t="n">
-        <v>102991</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104255</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2059,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127693676</v>
+        <v>4806382</v>
       </c>
       <c r="B14" t="n">
-        <v>98456</v>
+        <v>104628</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,41 +1920,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219798</v>
+        <v>222412</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hunneröd, 750m SSV, Sk</t>
+          <t>Havgård: 500 m väster om Gudmundtorp, Sk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>398773</v>
+        <v>398726</v>
       </c>
       <c r="R14" t="n">
-        <v>6149975</v>
+        <v>6150040</v>
       </c>
       <c r="S14" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2128,12 +1974,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2007-04-19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2007-04-19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2142,22 +1988,128 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Askskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
+          <t>Mats Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mats Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>118734410</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100460</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>224698</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lundäxing</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dactylis polygama</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Horv.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hunneröd, 750m SSV, Sk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>398773</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6149975</v>
+      </c>
+      <c r="S15" t="n">
+        <v>75</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Börringe</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>Ola Elleström</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>Ola Elleström</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25062-2026 artfynd.xlsx
+++ b/artfynd/A 25062-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/501842</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61734913</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2217567</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127693676</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1188,6 +1213,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2678987</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118734413</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1396,6 +1431,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2430227</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1498,6 +1538,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3440992</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1600,6 +1645,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3924727</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1702,6 +1752,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3784396</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1804,6 +1859,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4755275</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1906,6 +1966,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118734419</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2008,6 +2073,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4806382</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2110,8 +2180,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118734410</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>